--- a/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497628075552</v>
+        <v>10.84497629302412</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907176259989</v>
+        <v>37.78907180534956</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.372123437638546</v>
+        <v>4.558254590817941</v>
       </c>
       <c r="C2" t="n">
-        <v>10.2955881744363</v>
+        <v>9.974556675147593</v>
       </c>
       <c r="D2" t="n">
-        <v>18.77297960060751</v>
+        <v>20.82777754559608</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.33489914033518</v>
+        <v>12.73817646260236</v>
       </c>
       <c r="C3" t="n">
-        <v>12.64981916922015</v>
+        <v>21.89788254322511</v>
       </c>
       <c r="D3" t="n">
-        <v>49.09720268938299</v>
+        <v>62.16426463290804</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.35349559345364</v>
+        <v>29.25215459573796</v>
       </c>
       <c r="C4" t="n">
-        <v>46.46906408511428</v>
+        <v>68.21673922958962</v>
       </c>
       <c r="D4" t="n">
-        <v>65.47275439621978</v>
+        <v>81.75798531426587</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.58959806855839</v>
+        <v>37.84637399871455</v>
       </c>
       <c r="C5" t="n">
-        <v>97.58572180213298</v>
+        <v>109.5875874865502</v>
       </c>
       <c r="D5" t="n">
-        <v>53.13709449235862</v>
+        <v>61.62921213409354</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.58625191481815</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C6" t="n">
-        <v>117.6958417759246</v>
+        <v>120.0304378166235</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>45.96739100824416</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.96137734883166</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="C7" t="n">
-        <v>103.4840620092478</v>
+        <v>110.251248934621</v>
       </c>
       <c r="D7" t="n">
-        <v>38.14777054391831</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>65.84090978531233</v>
+        <v>80.86164966028853</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.717818371223281</v>
+        <v>7.695738469196087</v>
       </c>
       <c r="C21" t="n">
-        <v>96.47272964029102</v>
+        <v>94.27279624765205</v>
       </c>
       <c r="D21" t="n">
-        <v>8.682545667626192</v>
+        <v>8.657705777845598</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.041495445485625</v>
+        <v>6.193846266093127</v>
       </c>
       <c r="C2" t="n">
-        <v>11.52866329097029</v>
+        <v>8.93488585635022</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04804888424586</v>
+        <v>19.43075056245287</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76825078853552</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="C3" t="n">
-        <v>27.24349879284899</v>
+        <v>30.64525458806419</v>
       </c>
       <c r="D3" t="n">
-        <v>52.16516426515427</v>
+        <v>63.69088231301183</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.92407093607028</v>
+        <v>26.54645792283375</v>
       </c>
       <c r="C4" t="n">
-        <v>38.27539774547039</v>
+        <v>61.27381946515618</v>
       </c>
       <c r="D4" t="n">
-        <v>74.21521770253763</v>
+        <v>91.5214662330004</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.01942363656924</v>
+        <v>40.61981126321179</v>
       </c>
       <c r="C5" t="n">
-        <v>91.52342972840891</v>
+        <v>116.4107340310656</v>
       </c>
       <c r="D5" t="n">
-        <v>62.88094045700822</v>
+        <v>75.3491363009427</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.67683474551611</v>
+        <v>43.67304662341937</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2455637370406</v>
+        <v>146.3147691024234</v>
       </c>
       <c r="D6" t="n">
-        <v>48.22148373719484</v>
+        <v>53.33344403320799</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.14210104187108</v>
+        <v>33.47661496711198</v>
       </c>
       <c r="C7" t="n">
-        <v>137.0804501962779</v>
+        <v>139.8951208643535</v>
       </c>
       <c r="D7" t="n">
-        <v>41.02232782195297</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C8" t="n">
-        <v>100.4720600526186</v>
+        <v>112.9058947269044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.909159888247856</v>
+        <v>7.879837974702674</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7850135053151</v>
+        <v>103.4228734179726</v>
       </c>
       <c r="D21" t="n">
-        <v>9.886449860309821</v>
+        <v>9.849797468378343</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.303041245442774</v>
+        <v>5.753041546886309</v>
       </c>
       <c r="C2" t="n">
-        <v>7.511351685192347</v>
+        <v>8.474446183058467</v>
       </c>
       <c r="D2" t="n">
-        <v>20.92104357749953</v>
+        <v>20.30450601923253</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4364611222291</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C3" t="n">
-        <v>35.73070769606266</v>
+        <v>32.38785676310228</v>
       </c>
       <c r="D3" t="n">
-        <v>52.97510612115789</v>
+        <v>63.79396582195774</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.92407093607028</v>
+        <v>26.07423727709104</v>
       </c>
       <c r="C4" t="n">
-        <v>52.11018639371645</v>
+        <v>68.29331555052087</v>
       </c>
       <c r="D4" t="n">
-        <v>80.67315410107314</v>
+        <v>100.1107768974558</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.11759840699392</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="C5" t="n">
-        <v>81.53414683769762</v>
+        <v>113.4654909183251</v>
       </c>
       <c r="D5" t="n">
-        <v>73.21383504420589</v>
+        <v>86.81104074802423</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.43282153551517</v>
+        <v>48.38249036069132</v>
       </c>
       <c r="C6" t="n">
-        <v>139.0292193892078</v>
+        <v>163.7839877517912</v>
       </c>
       <c r="D6" t="n">
-        <v>54.98376192404687</v>
+        <v>62.71207985187777</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.76577287597506</v>
+        <v>41.3816474817073</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3107853583442</v>
+        <v>170.4372919434718</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>47.37030847761284</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.37942194439155</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="C8" t="n">
-        <v>138.5246010692249</v>
+        <v>144.6997941289374</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.41718602104266</v>
+        <v>14.31093628480575</v>
       </c>
       <c r="C9" t="n">
-        <v>89.1937424262312</v>
+        <v>102.2843663146582</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>53.80959166976768</v>
+        <v>60.64255569132548</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>40.33706792438868</v>
       </c>
       <c r="D11" t="n">
         <v>36.96083756948391</v>
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.086160122794885</v>
+        <v>8.048931552920109</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2170117344778</v>
+        <v>111.6789252967665</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11847016884296</v>
+        <v>11.06728088526515</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.292822857772807</v>
+        <v>5.328926538651687</v>
       </c>
       <c r="C2" t="n">
-        <v>4.927391727614741</v>
+        <v>5.6941366846315</v>
       </c>
       <c r="D2" t="n">
-        <v>16.87427954059418</v>
+        <v>16.73290787118264</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.19517217116264</v>
+        <v>19.3453385121834</v>
       </c>
       <c r="C3" t="n">
-        <v>47.40368789955724</v>
+        <v>46.85390918517903</v>
       </c>
       <c r="D3" t="n">
-        <v>59.40064484545326</v>
+        <v>70.24895697738052</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.15608218944201</v>
+        <v>19.47591095684822</v>
       </c>
       <c r="C4" t="n">
-        <v>70.70546965985528</v>
+        <v>95.31199411909735</v>
       </c>
       <c r="D4" t="n">
-        <v>79.38411936539708</v>
+        <v>97.07324950051611</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.78408192499049</v>
+        <v>27.243498792849</v>
       </c>
       <c r="C5" t="n">
-        <v>83.05585577928017</v>
+        <v>97.85570242080085</v>
       </c>
       <c r="D5" t="n">
-        <v>53.23526926278331</v>
+        <v>61.62921213409354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.87302005544945</v>
+        <v>25.68055644768807</v>
       </c>
       <c r="C6" t="n">
-        <v>107.5524244956466</v>
+        <v>112.2618682329185</v>
       </c>
       <c r="D6" t="n">
-        <v>29.66547037922588</v>
+        <v>31.19503330244241</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>97.37562779342413</v>
+        <v>101.7473503204352</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>65.67401267559038</v>
+        <v>75.35404503946393</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
         <v>28.89774367450487</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.828235209485814</v>
+        <v>3.363467634749572</v>
       </c>
       <c r="C2" t="n">
-        <v>2.272745935331366</v>
+        <v>3.082687791334985</v>
       </c>
       <c r="D2" t="n">
-        <v>11.51590057081509</v>
+        <v>11.71519535477719</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.12078032981814</v>
+        <v>19.44842202112931</v>
       </c>
       <c r="C3" t="n">
-        <v>32.93763547748049</v>
+        <v>34.78332116146449</v>
       </c>
       <c r="D3" t="n">
-        <v>60.04859833025616</v>
+        <v>68.02529842726149</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>27.27393297168064</v>
       </c>
       <c r="C4" t="n">
-        <v>97.67309734781091</v>
+        <v>108.5341721998934</v>
       </c>
       <c r="D4" t="n">
-        <v>89.24970204537328</v>
+        <v>109.121257327033</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>29.94330497952772</v>
       </c>
       <c r="C5" t="n">
-        <v>108.1640533153924</v>
+        <v>136.5856493533375</v>
       </c>
       <c r="D5" t="n">
-        <v>65.99798941799185</v>
+        <v>76.52723354603889</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.11202671593793</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="C6" t="n">
-        <v>123.4518285659237</v>
+        <v>136.2116034780195</v>
       </c>
       <c r="D6" t="n">
-        <v>36.50825187782615</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>124.3246022749991</v>
+        <v>127.5584792127881</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>88.20512248805467</v>
+        <v>98.21894907137214</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>47.92499593051228</v>
+        <v>52.58437053486764</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2184,7 +2184,7 @@
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.722607368054658</v>
+        <v>3.346777923777377</v>
       </c>
       <c r="C2" t="n">
-        <v>5.451645001682538</v>
+        <v>8.855364292306231</v>
       </c>
       <c r="D2" t="n">
-        <v>15.33195389722244</v>
+        <v>13.26635672748715</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.62790192455724</v>
+        <v>15.52633994266331</v>
       </c>
       <c r="C3" t="n">
-        <v>19.45333075965055</v>
+        <v>22.5605622435917</v>
       </c>
       <c r="D3" t="n">
-        <v>55.55710258332701</v>
+        <v>61.98264130762237</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.04865508351838</v>
+        <v>32.03442758957343</v>
       </c>
       <c r="C4" t="n">
-        <v>90.33453325856601</v>
+        <v>97.23916486253384</v>
       </c>
       <c r="D4" t="n">
-        <v>98.0815043927776</v>
+        <v>117.506364469005</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.11697651218817</v>
+        <v>35.29382996767284</v>
       </c>
       <c r="C5" t="n">
-        <v>144.9059611468292</v>
+        <v>168.3451875857218</v>
       </c>
       <c r="D5" t="n">
-        <v>81.2150788338174</v>
+        <v>95.94129439751956</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>35.783722072092</v>
       </c>
       <c r="C6" t="n">
-        <v>148.7701201107447</v>
+        <v>176.6242659756352</v>
       </c>
       <c r="D6" t="n">
-        <v>47.01393406097126</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.66194429903638</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>150.9741437067787</v>
+        <v>161.8735067193268</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>125.6735236206342</v>
+        <v>131.8487166803466</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>76.65780599070366</v>
+        <v>82.87030546317747</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.29965403397353</v>
+        <v>1.956623174563893</v>
       </c>
       <c r="C2" t="n">
-        <v>2.449460522095792</v>
+        <v>4.102723656047421</v>
       </c>
       <c r="D2" t="n">
-        <v>10.57636801785089</v>
+        <v>9.205848222722341</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.57037972063417</v>
+        <v>15.25635932399543</v>
       </c>
       <c r="C3" t="n">
-        <v>21.57390580082366</v>
+        <v>29.30516897176729</v>
       </c>
       <c r="D3" t="n">
-        <v>56.58302893426492</v>
+        <v>60.98125864929062</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.97506506342888</v>
+        <v>35.67180283380785</v>
       </c>
       <c r="C4" t="n">
-        <v>82.9959691693211</v>
+        <v>91.58527983377644</v>
       </c>
       <c r="D4" t="n">
-        <v>104.2586609478985</v>
+        <v>123.7600973450572</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>37.50276230222816</v>
       </c>
       <c r="C5" t="n">
-        <v>172.3212657879214</v>
+        <v>195.7850359194202</v>
       </c>
       <c r="D5" t="n">
-        <v>88.01368168572657</v>
+        <v>104.1388877279804</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.15227837181205</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>189.5047958553534</v>
+        <v>217.7614582789851</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>50.15356321915257</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8735067193268</v>
+        <v>172.4734366820796</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>98.30239762623312</v>
+        <v>102.3913768144211</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.705115835827462</v>
+        <v>2.254092728950677</v>
       </c>
       <c r="C2" t="n">
-        <v>5.188536616944393</v>
+        <v>8.015970005175207</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13796876240907</v>
+        <v>9.168541809960962</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.01859645311846</v>
+        <v>11.08393158094649</v>
       </c>
       <c r="C3" t="n">
-        <v>15.13364086096458</v>
+        <v>22.43293504203962</v>
       </c>
       <c r="D3" t="n">
-        <v>52.70021676396878</v>
+        <v>54.84533549774806</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.83092807735385</v>
+        <v>32.65980087717864</v>
       </c>
       <c r="C4" t="n">
-        <v>68.62514627455629</v>
+        <v>82.28125684062942</v>
       </c>
       <c r="D4" t="n">
-        <v>108.0747142743059</v>
+        <v>125.6745053683384</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.21134746498289</v>
+        <v>45.18493808795945</v>
       </c>
       <c r="C5" t="n">
-        <v>164.3936530761284</v>
+        <v>184.519481013188</v>
       </c>
       <c r="D5" t="n">
-        <v>102.5926350937917</v>
+        <v>121.515822093149</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.45670227558657</v>
+        <v>38.27932473628739</v>
       </c>
       <c r="C6" t="n">
-        <v>230.6419881587032</v>
+        <v>262.4810479551315</v>
       </c>
       <c r="D6" t="n">
-        <v>60.17622553180826</v>
+        <v>67.34102027740147</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>215.5319092426405</v>
+        <v>238.1091611972044</v>
       </c>
       <c r="D7" t="n">
-        <v>39.04606969330414</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>148.7887733171253</v>
+        <v>155.7150033705866</v>
       </c>
       <c r="D8" t="n">
         <v>33.96356182841841</v>
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>69.89061906533041</v>
       </c>
       <c r="D9" t="n">
         <v>33.28124717396686</v>
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.1301147807751</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>14.13520344574558</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.701769682087222</v>
+        <v>1.519745446174062</v>
       </c>
       <c r="C2" t="n">
-        <v>3.765002445786517</v>
+        <v>4.086033945075225</v>
       </c>
       <c r="D2" t="n">
-        <v>11.74661128131308</v>
+        <v>6.953718989180158</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.33980787885641</v>
+        <v>9.758572180213296</v>
       </c>
       <c r="C3" t="n">
-        <v>17.74018101573986</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="D3" t="n">
-        <v>53.32853529468674</v>
+        <v>50.78090000216627</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.33845058272045</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C4" t="n">
-        <v>56.52608756741861</v>
+        <v>73.04104744825845</v>
       </c>
       <c r="D4" t="n">
-        <v>111.022902630159</v>
+        <v>125.3299119241478</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.69088231301183</v>
+        <v>48.20381227851841</v>
       </c>
       <c r="C5" t="n">
-        <v>154.821612959722</v>
+        <v>176.3955187605457</v>
       </c>
       <c r="D5" t="n">
-        <v>112.581917984503</v>
+        <v>133.9840179370835</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.35231822376692</v>
+        <v>45.32336451425826</v>
       </c>
       <c r="C6" t="n">
-        <v>252.9816571688394</v>
+        <v>286.1892732649877</v>
       </c>
       <c r="D6" t="n">
-        <v>71.56744414418399</v>
+        <v>79.21525876026665</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>16.40893112878119</v>
       </c>
       <c r="C7" t="n">
-        <v>263.9801766995163</v>
+        <v>293.1449557495764</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>44.49575119957818</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>189.511668089283</v>
+        <v>200.7772229955152</v>
       </c>
       <c r="D8" t="n">
         <v>35.88287859022092</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>83.53593040665682</v>
+        <v>83.20311793491715</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.941136195474197</v>
+        <v>2.987458264023044</v>
       </c>
       <c r="C2" t="n">
-        <v>5.237624002156734</v>
+        <v>7.142214548395546</v>
       </c>
       <c r="D2" t="n">
-        <v>19.7900702222072</v>
+        <v>12.33467815615692</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.31602494977624</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C3" t="n">
-        <v>16.10066234964769</v>
+        <v>21.61808444751476</v>
       </c>
       <c r="D3" t="n">
-        <v>50.52073686054086</v>
+        <v>45.60708960078558</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>24.31298189567226</v>
       </c>
       <c r="C4" t="n">
-        <v>50.65523629602267</v>
+        <v>70.30982533504381</v>
       </c>
       <c r="D4" t="n">
-        <v>111.8907676007132</v>
+        <v>122.4838253295363</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.78905708343652</v>
+        <v>46.4612101034803</v>
       </c>
       <c r="C5" t="n">
-        <v>131.6769108321035</v>
+        <v>157.8895745354933</v>
       </c>
       <c r="D5" t="n">
-        <v>123.675667042492</v>
+        <v>142.991553123548</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.26680836250623</v>
+        <v>53.09193409796327</v>
       </c>
       <c r="C6" t="n">
-        <v>251.0495776868817</v>
+        <v>284.9414719328901</v>
       </c>
       <c r="D6" t="n">
-        <v>85.8165303236222</v>
+        <v>97.04674231250146</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.08788393395925</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="C7" t="n">
-        <v>311.5900316169654</v>
+        <v>343.6892545550191</v>
       </c>
       <c r="D7" t="n">
-        <v>50.84373185523806</v>
+        <v>53.35896947351839</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>255.7698206489002</v>
+        <v>277.9671362419206</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>143.6640503009569</v>
+        <v>145.1062376784955</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>56.22959976073607</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.050110190645593</v>
+        <v>4.288273972150068</v>
       </c>
       <c r="C2" t="n">
-        <v>5.561600744558181</v>
+        <v>8.810203897910876</v>
       </c>
       <c r="D2" t="n">
-        <v>5.757950285407543</v>
+        <v>11.5895316486336</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.455751918948773</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C2" t="n">
-        <v>2.891246989006857</v>
+        <v>4.05658151394782</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56520894020568</v>
+        <v>9.078221021170256</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23948968657399</v>
+        <v>10.68632376072653</v>
       </c>
       <c r="C3" t="n">
-        <v>19.93929587325272</v>
+        <v>26.75262494072558</v>
       </c>
       <c r="D3" t="n">
-        <v>57.30952223540756</v>
+        <v>50.89380098815465</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.43452298901639</v>
+        <v>34.701836102012</v>
       </c>
       <c r="C4" t="n">
-        <v>73.564318974622</v>
+        <v>98.64306407960677</v>
       </c>
       <c r="D4" t="n">
-        <v>115.7833972480518</v>
+        <v>126.4785567381166</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.40520942660923</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C5" t="n">
-        <v>205.4797944988575</v>
+        <v>237.5829444277282</v>
       </c>
       <c r="D5" t="n">
-        <v>115.3553552490002</v>
+        <v>133.3213382367169</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.62772199810799</v>
+        <v>18.15349679922777</v>
       </c>
       <c r="C6" t="n">
-        <v>259.3414187969502</v>
+        <v>285.0219752446383</v>
       </c>
       <c r="D6" t="n">
-        <v>71.68819911180636</v>
+        <v>78.12846405166543</v>
       </c>
     </row>
     <row r="7">
@@ -4271,10 +4271,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8394897070435</v>
+        <v>195.4698949063569</v>
       </c>
       <c r="D7" t="n">
         <v>33.89582123682538</v>
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>105.8962161185822</v>
+        <v>106.8975987769139</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.20360698987336</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.49921085984289</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.442629345895069</v>
+        <v>5.735370088209866</v>
       </c>
       <c r="C2" t="n">
-        <v>4.98924183298229</v>
+        <v>5.552765015219959</v>
       </c>
       <c r="D2" t="n">
-        <v>7.386669726753001</v>
+        <v>13.72974164389164</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.73050240741764</v>
+        <v>9.115527433931634</v>
       </c>
       <c r="C3" t="n">
-        <v>14.23534171157875</v>
+        <v>22.19731559302038</v>
       </c>
       <c r="D3" t="n">
-        <v>8.202502068982101</v>
+        <v>12.87071240267569</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3991933482784</v>
+        <v>13.39776373172912</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14871811745749</v>
+        <v>70.14123365434654</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576375688032752</v>
+        <v>1.576207497850484</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.945063186291184</v>
+        <v>3.754203221039802</v>
       </c>
       <c r="C2" t="n">
-        <v>5.560618996853934</v>
+        <v>4.592615760466579</v>
       </c>
       <c r="D2" t="n">
-        <v>17.91591385480004</v>
+        <v>14.9579080219044</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.65949777754238</v>
+        <v>15.50179625005713</v>
       </c>
       <c r="C3" t="n">
-        <v>17.56346642897544</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D3" t="n">
-        <v>12.42401719724339</v>
+        <v>21.29410770511332</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.54575391256999</v>
+        <v>10.73344765053038</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5772519545639</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="D4" t="n">
-        <v>19.37380919560656</v>
+        <v>21.81148874525138</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44548915057824</v>
+        <v>15.44080662144571</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1695710505944</v>
+        <v>86.14344746701292</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251681926437524</v>
+        <v>3.250696130830676</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.945063186291184</v>
+        <v>5.427101309076368</v>
       </c>
       <c r="C2" t="n">
-        <v>8.224100518475531</v>
+        <v>5.711808143307943</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9304601439145</v>
+        <v>18.52852442225005</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.23105486786327</v>
+        <v>14.09298829446296</v>
       </c>
       <c r="C3" t="n">
-        <v>20.03256190515617</v>
+        <v>19.43860454408685</v>
       </c>
       <c r="D3" t="n">
-        <v>23.8711954287612</v>
+        <v>28.31851252899925</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.89105136702439</v>
+        <v>21.56899706230242</v>
       </c>
       <c r="C4" t="n">
-        <v>34.95709050511617</v>
+        <v>46.36696232387261</v>
       </c>
       <c r="D4" t="n">
-        <v>21.26269177857742</v>
+        <v>27.58023825540564</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.388273369263</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C5" t="n">
-        <v>26.43355693684537</v>
+        <v>38.50905369908114</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>30.26237298340794</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,7 +5274,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74365346628621</v>
+        <v>16.73556329958457</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1362861443459</v>
+        <v>102.0869361274659</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023096039885862</v>
+        <v>5.020668989875372</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.855724145204724</v>
+        <v>4.574944301790136</v>
       </c>
       <c r="C2" t="n">
-        <v>5.500732386894879</v>
+        <v>8.35663645854885</v>
       </c>
       <c r="D2" t="n">
-        <v>15.89253183634737</v>
+        <v>23.89181213055037</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5291052593268</v>
+        <v>16.56208377064369</v>
       </c>
       <c r="C3" t="n">
-        <v>27.01769682087222</v>
+        <v>21.00449213236051</v>
       </c>
       <c r="D3" t="n">
-        <v>33.70830742531424</v>
+        <v>36.09886308515522</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>24.77243982125977</v>
       </c>
       <c r="C4" t="n">
-        <v>43.59745205019236</v>
+        <v>47.19653913396116</v>
       </c>
       <c r="D4" t="n">
-        <v>27.84825537866502</v>
+        <v>35.1357685872891</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.13903262557133</v>
+        <v>21.05848825609409</v>
       </c>
       <c r="C5" t="n">
-        <v>47.41841411512095</v>
+        <v>64.45173678380311</v>
       </c>
       <c r="D5" t="n">
-        <v>30.60598467989432</v>
+        <v>32.98672286269284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>27.77364255314227</v>
+        <v>37.91705983342032</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.52083467153211</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07598925374805</v>
+        <v>18.06352037220301</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9243108458801</v>
+        <v>117.8429662377053</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886091144284972</v>
+        <v>6.881341094172574</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.586144437164351</v>
+        <v>4.818417732443345</v>
       </c>
       <c r="C2" t="n">
-        <v>6.167339078078462</v>
+        <v>8.929977117828987</v>
       </c>
       <c r="D2" t="n">
-        <v>16.31762859228623</v>
+        <v>23.27429282457913</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.21708941582556</v>
+        <v>14.28933783531232</v>
       </c>
       <c r="C3" t="n">
-        <v>22.32003405605123</v>
+        <v>25.90341317655209</v>
       </c>
       <c r="D3" t="n">
-        <v>36.02032326881547</v>
+        <v>43.48651455961247</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.03220205225767</v>
+        <v>20.87981017392116</v>
       </c>
       <c r="C4" t="n">
-        <v>48.01335322389451</v>
+        <v>41.64475586644545</v>
       </c>
       <c r="D4" t="n">
-        <v>32.85124167950677</v>
+        <v>38.76038111136832</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.48202242725196</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="C5" t="n">
-        <v>48.40016181936777</v>
+        <v>57.18680377237672</v>
       </c>
       <c r="D5" t="n">
-        <v>27.43984833369836</v>
+        <v>31.04777114680538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>36.02523200733671</v>
+        <v>48.5434969841878</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>31.31578827006476</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>19.94224111636546</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.06806234306728</v>
+        <v>7.060864968469993</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14659225913915</v>
+        <v>66.19560907940618</v>
       </c>
       <c r="D21" t="n">
-        <v>5.30104675730046</v>
+        <v>5.295648726352495</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.513094196422587</v>
+        <v>4.226423866782518</v>
       </c>
       <c r="C2" t="n">
-        <v>2.712568906833937</v>
+        <v>6.052474596681586</v>
       </c>
       <c r="D2" t="n">
-        <v>17.77846917620549</v>
+        <v>24.75967710110456</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>15.93376523992573</v>
       </c>
       <c r="C3" t="n">
-        <v>23.53249247079604</v>
+        <v>31.80862561759665</v>
       </c>
       <c r="D3" t="n">
-        <v>41.32666961026948</v>
+        <v>53.04382846045517</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.02693346083794</v>
+        <v>25.30847406777853</v>
       </c>
       <c r="C4" t="n">
-        <v>53.25883120768522</v>
+        <v>56.56437572788423</v>
       </c>
       <c r="D4" t="n">
-        <v>44.68228326338508</v>
+        <v>53.27159392784043</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.63052837250049</v>
+        <v>26.04085785514665</v>
       </c>
       <c r="C5" t="n">
-        <v>73.95014582239101</v>
+        <v>69.60591223109887</v>
       </c>
       <c r="D5" t="n">
-        <v>33.52668410002858</v>
+        <v>38.85266539556753</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.34596040698915</v>
+        <v>18.6365166697172</v>
       </c>
       <c r="C6" t="n">
-        <v>60.94100699341652</v>
+        <v>73.98254349663115</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76484788153306</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>39.34550274309942</v>
+        <v>51.50248456478767</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>23.61594102565702</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295979137645211</v>
+        <v>7.285198331677115</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51977833748037</v>
+        <v>75.58393269115008</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383981745439559</v>
+        <v>6.374548540217476</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.101741908343174</v>
+        <v>3.080724295926491</v>
       </c>
       <c r="C2" t="n">
-        <v>2.756747553525043</v>
+        <v>4.69079053089126</v>
       </c>
       <c r="D2" t="n">
-        <v>17.26010638836317</v>
+        <v>19.8509385798705</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.88606051304514</v>
+        <v>15.37416904850505</v>
       </c>
       <c r="C3" t="n">
-        <v>15.42816517223863</v>
+        <v>26.80171232593792</v>
       </c>
       <c r="D3" t="n">
-        <v>46.2746780396734</v>
+        <v>60.54438092090079</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.13652935081509</v>
+        <v>28.49915410658066</v>
       </c>
       <c r="C4" t="n">
-        <v>56.78134197052277</v>
+        <v>69.64616388697297</v>
       </c>
       <c r="D4" t="n">
-        <v>55.97729060074463</v>
+        <v>67.38716241950105</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.47821860962199</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="C5" t="n">
-        <v>88.52909923045614</v>
+        <v>89.95263340161401</v>
       </c>
       <c r="D5" t="n">
-        <v>42.55876297909924</v>
+        <v>49.87278337573798</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.44912603139308</v>
+        <v>27.6126359296458</v>
       </c>
       <c r="C6" t="n">
-        <v>93.22283500446015</v>
+        <v>94.71214627180255</v>
       </c>
       <c r="D6" t="n">
-        <v>36.02523200733671</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>66.95322993422397</v>
+        <v>82.46386191361933</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>39.55461500410399</v>
+        <v>49.48499303256047</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.40156017323271</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.512976828596615</v>
+        <v>7.497122388386022</v>
       </c>
       <c r="C21" t="n">
-        <v>87.33835563243565</v>
+        <v>85.27976716789101</v>
       </c>
       <c r="D21" t="n">
-        <v>7.512976828596615</v>
+        <v>7.497122388386022</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629302412</v>
+        <v>10.84497642595035</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907180534956</v>
+        <v>37.78907226852798</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.558254590817941</v>
+        <v>5.644067551714913</v>
       </c>
       <c r="C2" t="n">
-        <v>9.974556675147593</v>
+        <v>13.20352487441535</v>
       </c>
       <c r="D2" t="n">
-        <v>20.82777754559608</v>
+        <v>34.38571334124453</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.73817646260236</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C3" t="n">
-        <v>21.89788254322511</v>
+        <v>43.8792136413112</v>
       </c>
       <c r="D3" t="n">
-        <v>62.16426463290804</v>
+        <v>72.35971454151115</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.25215459573796</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>68.21673922958962</v>
+        <v>74.81506554983244</v>
       </c>
       <c r="D4" t="n">
-        <v>81.75798531426587</v>
+        <v>93.57626417798897</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.84637399871455</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="C5" t="n">
-        <v>109.5875874865502</v>
+        <v>104.8506548135594</v>
       </c>
       <c r="D5" t="n">
-        <v>61.62921213409354</v>
+        <v>75.57002953439824</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.22649028670731</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>120.0304378166235</v>
+        <v>128.2417756149439</v>
       </c>
       <c r="D6" t="n">
-        <v>45.96739100824416</v>
+        <v>51.15985461600555</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>110.251248934621</v>
+        <v>117.737075179503</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>80.86164966028853</v>
+        <v>73.1009340582175</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>38.82812170296133</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.66110142005238</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695738469196087</v>
+        <v>7.680234074466925</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27279624765205</v>
+        <v>93.12283815291146</v>
       </c>
       <c r="D21" t="n">
-        <v>8.657705777845598</v>
+        <v>7.680234074466925</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.193846266093127</v>
+        <v>5.915029918087032</v>
       </c>
       <c r="C2" t="n">
-        <v>8.93488585635022</v>
+        <v>12.43677991739859</v>
       </c>
       <c r="D2" t="n">
-        <v>19.43075056245287</v>
+        <v>36.89015173477815</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95063487734718</v>
+        <v>17.24930716361646</v>
       </c>
       <c r="C3" t="n">
-        <v>30.64525458806419</v>
+        <v>47.35950925286613</v>
       </c>
       <c r="D3" t="n">
-        <v>63.69088231301183</v>
+        <v>81.03836424705297</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.54645792283375</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="C4" t="n">
-        <v>61.27381946515618</v>
+        <v>91.01095742679206</v>
       </c>
       <c r="D4" t="n">
-        <v>91.5214662330004</v>
+        <v>106.1603062510246</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.61981126321179</v>
+        <v>43.81049130201392</v>
       </c>
       <c r="C5" t="n">
-        <v>116.4107340310656</v>
+        <v>120.6322491593268</v>
       </c>
       <c r="D5" t="n">
-        <v>75.3491363009427</v>
+        <v>88.57818661566847</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.67304662341937</v>
+        <v>45.12210623488766</v>
       </c>
       <c r="C6" t="n">
-        <v>146.3147691024234</v>
+        <v>145.0267161144516</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33344403320799</v>
+        <v>61.62528514327655</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.47661496711198</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8951208643535</v>
+        <v>149.8961847275158</v>
       </c>
       <c r="D7" t="n">
-        <v>43.35790561035613</v>
+        <v>44.97484407925062</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.61041039233004</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9058947269044</v>
+        <v>110.652783745658</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>62.79061966821748</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.879837974702674</v>
+        <v>7.857108752642118</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4228734179726</v>
+        <v>101.1602751902673</v>
       </c>
       <c r="D21" t="n">
-        <v>9.849797468378343</v>
+        <v>8.839247346722383</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.753041546886309</v>
+        <v>5.942518853805943</v>
       </c>
       <c r="C2" t="n">
-        <v>8.474446183058467</v>
+        <v>19.20102159965912</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30450601923253</v>
+        <v>41.71151471033424</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91060420565131</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>32.38785676310228</v>
+        <v>47.34478303730243</v>
       </c>
       <c r="D3" t="n">
-        <v>63.79396582195774</v>
+        <v>88.25911861178827</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.07423727709104</v>
+        <v>30.93683365622549</v>
       </c>
       <c r="C4" t="n">
-        <v>68.29331555052087</v>
+        <v>101.8082186780985</v>
       </c>
       <c r="D4" t="n">
-        <v>100.1107768974558</v>
+        <v>116.957567502331</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.54618018539328</v>
+        <v>44.47317100238052</v>
       </c>
       <c r="C5" t="n">
-        <v>113.4654909183251</v>
+        <v>139.4081740030471</v>
       </c>
       <c r="D5" t="n">
-        <v>86.81104074802423</v>
+        <v>102.5190040159732</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.38249036069132</v>
+        <v>51.15985461600555</v>
       </c>
       <c r="C6" t="n">
-        <v>163.7839877517912</v>
+        <v>165.0317890838888</v>
       </c>
       <c r="D6" t="n">
-        <v>62.71207985187777</v>
+        <v>71.44668917656163</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.3816474817073</v>
+        <v>42.4596064609703</v>
       </c>
       <c r="C7" t="n">
-        <v>170.4372919434718</v>
+        <v>174.1502617609332</v>
       </c>
       <c r="D7" t="n">
-        <v>47.37030847761284</v>
+        <v>50.90361846519711</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.37112599440107</v>
       </c>
       <c r="C8" t="n">
-        <v>144.6997941289374</v>
+        <v>147.0363536650448</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2843663146582</v>
+        <v>94.07499201174633</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>60.64255569132548</v>
+        <v>52.10135066437823</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.048931552920109</v>
+        <v>8.016516919436517</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6789252967665</v>
+        <v>109.2250430273226</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06728088526515</v>
+        <v>10.02064614929565</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.328926538651687</v>
+        <v>5.589089680277091</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6941366846315</v>
+        <v>13.36354975020758</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73290787118264</v>
+        <v>34.21587098840983</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3453385121834</v>
+        <v>21.33828635180442</v>
       </c>
       <c r="C3" t="n">
-        <v>46.85390918517903</v>
+        <v>71.97192419833367</v>
       </c>
       <c r="D3" t="n">
-        <v>70.24895697738052</v>
+        <v>94.30668446994861</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.47591095684822</v>
+        <v>21.36479353981909</v>
       </c>
       <c r="C4" t="n">
-        <v>95.31199411909735</v>
+        <v>124.3216570318863</v>
       </c>
       <c r="D4" t="n">
-        <v>97.07324950051611</v>
+        <v>113.1925650565445</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.243498792849</v>
+        <v>28.81429511964389</v>
       </c>
       <c r="C5" t="n">
-        <v>97.85570242080085</v>
+        <v>98.61655689159213</v>
       </c>
       <c r="D5" t="n">
-        <v>61.62921213409354</v>
+        <v>70.24404823885929</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.68055644768807</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="C6" t="n">
-        <v>112.2618682329185</v>
+        <v>114.6769675853657</v>
       </c>
       <c r="D6" t="n">
-        <v>31.19503330244241</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>101.7473503204352</v>
+        <v>103.3642887893297</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>28.56591295046944</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>75.35404503946393</v>
+        <v>69.34574908947344</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>39.71562162760046</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>28.60910984945629</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.363467634749572</v>
+        <v>3.446916189610551</v>
       </c>
       <c r="C2" t="n">
-        <v>3.082687791334985</v>
+        <v>6.304783756673016</v>
       </c>
       <c r="D2" t="n">
-        <v>11.71519535477719</v>
+        <v>24.24229606096649</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44842202112931</v>
+        <v>20.89649988489336</v>
       </c>
       <c r="C3" t="n">
-        <v>34.78332116146449</v>
+        <v>63.3423618780042</v>
       </c>
       <c r="D3" t="n">
-        <v>68.02529842726149</v>
+        <v>100.2168056495144</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.27393297168064</v>
+        <v>29.43083267791088</v>
       </c>
       <c r="C4" t="n">
-        <v>108.5341721998934</v>
+        <v>154.8373209229899</v>
       </c>
       <c r="D4" t="n">
-        <v>109.121257327033</v>
+        <v>129.8351521389364</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.94330497952772</v>
+        <v>31.80862561759666</v>
       </c>
       <c r="C5" t="n">
-        <v>136.5856493533375</v>
+        <v>155.6315548157257</v>
       </c>
       <c r="D5" t="n">
-        <v>76.52723354603889</v>
+        <v>88.52909923045614</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.91327171132357</v>
       </c>
       <c r="C6" t="n">
-        <v>136.2116034780195</v>
+        <v>137.4996564659913</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>41.13719230334986</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>127.5584792127881</v>
+        <v>128.516664972133</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>98.21894907137214</v>
+        <v>91.79341034707677</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>52.58437053486764</v>
+        <v>43.4874963073167</v>
       </c>
       <c r="D9" t="n">
         <v>28.51093507903161</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.346777923777377</v>
+        <v>3.295727043156542</v>
       </c>
       <c r="C2" t="n">
-        <v>8.855364292306231</v>
+        <v>6.843763246304515</v>
       </c>
       <c r="D2" t="n">
-        <v>13.26635672748715</v>
+        <v>19.86664654313845</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.52633994266331</v>
+        <v>16.33137306014569</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5605622435917</v>
+        <v>43.61905049968578</v>
       </c>
       <c r="D3" t="n">
-        <v>61.98264130762237</v>
+        <v>96.33399347921828</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.03442758957343</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>97.23916486253384</v>
+        <v>156.2412201400629</v>
       </c>
       <c r="D4" t="n">
-        <v>117.506364469005</v>
+        <v>147.2179769903304</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.29382996767284</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C5" t="n">
-        <v>168.3451875857218</v>
+        <v>216.5244561716341</v>
       </c>
       <c r="D5" t="n">
-        <v>95.94129439751956</v>
+        <v>110.569335190797</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.783722072092</v>
+        <v>36.06548366321083</v>
       </c>
       <c r="C6" t="n">
-        <v>176.6242659756352</v>
+        <v>188.377749490878</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>55.54728510628455</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>24.61339669317178</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8735067193268</v>
+        <v>159.7175887608009</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>131.8487166803466</v>
+        <v>126.8418033886879</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>82.87030546317747</v>
+        <v>72.77499382040753</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>29.07347651356504</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.956623174563893</v>
+        <v>1.998838325846506</v>
       </c>
       <c r="C2" t="n">
-        <v>4.102723656047421</v>
+        <v>3.344814428368883</v>
       </c>
       <c r="D2" t="n">
-        <v>9.205848222722341</v>
+        <v>13.85933234085222</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.25635932399543</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C3" t="n">
-        <v>29.30516897176729</v>
+        <v>39.42207906403067</v>
       </c>
       <c r="D3" t="n">
-        <v>60.98125864929062</v>
+        <v>94.48339905671304</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.67180283380785</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="C4" t="n">
-        <v>91.58527983377644</v>
+        <v>154.8245582028347</v>
       </c>
       <c r="D4" t="n">
-        <v>123.7600973450572</v>
+        <v>159.8275445036765</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.50276230222816</v>
+        <v>38.60722846950583</v>
       </c>
       <c r="C5" t="n">
-        <v>195.7850359194202</v>
+        <v>268.3116475706533</v>
       </c>
       <c r="D5" t="n">
-        <v>104.1388877279804</v>
+        <v>116.1407534123977</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.22899356146354</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>217.7614582789851</v>
+        <v>216.8759218497544</v>
       </c>
       <c r="D6" t="n">
-        <v>50.15356321915257</v>
+        <v>53.65545728020094</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4734366820796</v>
+        <v>165.0474970471568</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3913768144211</v>
+        <v>89.62374792069132</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.27821981539612</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>20.82875929330033</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.254092728950677</v>
+        <v>2.525055095322796</v>
       </c>
       <c r="C2" t="n">
-        <v>8.015970005175207</v>
+        <v>9.393362034233482</v>
       </c>
       <c r="D2" t="n">
-        <v>9.168541809960962</v>
+        <v>17.621389543526</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.08393158094649</v>
+        <v>11.59934912567607</v>
       </c>
       <c r="C3" t="n">
-        <v>22.43293504203962</v>
+        <v>26.34519964346316</v>
       </c>
       <c r="D3" t="n">
-        <v>54.84533549774806</v>
+        <v>85.05862109594365</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.65980087717864</v>
+        <v>34.34447993766616</v>
       </c>
       <c r="C4" t="n">
-        <v>82.28125684062942</v>
+        <v>129.4777959745906</v>
       </c>
       <c r="D4" t="n">
-        <v>125.6745053683384</v>
+        <v>168.1488380448725</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.18493808795945</v>
+        <v>45.23402547317179</v>
       </c>
       <c r="C5" t="n">
-        <v>184.519481013188</v>
+        <v>277.7364255314227</v>
       </c>
       <c r="D5" t="n">
-        <v>121.515822093149</v>
+        <v>141.2489509485099</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.27932473628739</v>
+        <v>37.79630486579796</v>
       </c>
       <c r="C6" t="n">
-        <v>262.4810479551315</v>
+        <v>304.9465449023273</v>
       </c>
       <c r="D6" t="n">
-        <v>67.34102027740147</v>
+        <v>70.03788122096746</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>238.1091611972044</v>
+        <v>226.910365134861</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>155.7150033705866</v>
+        <v>138.1073582949201</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>69.89061906533041</v>
+        <v>56.91093266748334</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.519745446174062</v>
+        <v>1.715113239319178</v>
       </c>
       <c r="C2" t="n">
-        <v>4.086033945075225</v>
+        <v>5.579272203234622</v>
       </c>
       <c r="D2" t="n">
-        <v>6.953718989180158</v>
+        <v>13.17407244328795</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.758572180213296</v>
+        <v>10.44579557318606</v>
       </c>
       <c r="C3" t="n">
-        <v>27.02260555939346</v>
+        <v>31.20485077948487</v>
       </c>
       <c r="D3" t="n">
-        <v>50.78090000216627</v>
+        <v>80.90582830697964</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.03518835309942</v>
+        <v>30.33698580893068</v>
       </c>
       <c r="C4" t="n">
-        <v>73.04104744825845</v>
+        <v>107.6790699494944</v>
       </c>
       <c r="D4" t="n">
-        <v>125.3299119241478</v>
+        <v>172.8710445022996</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.20381227851841</v>
+        <v>48.866491978885</v>
       </c>
       <c r="C5" t="n">
-        <v>176.3955187605457</v>
+        <v>270.569667290421</v>
       </c>
       <c r="D5" t="n">
-        <v>133.9840179370835</v>
+        <v>155.7788169713627</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.32336451425826</v>
+        <v>42.74725853831463</v>
       </c>
       <c r="C6" t="n">
-        <v>286.1892732649877</v>
+        <v>359.8900551705</v>
       </c>
       <c r="D6" t="n">
-        <v>79.21525876026665</v>
+        <v>82.95866275655973</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.40893112878119</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>293.1449557495764</v>
+        <v>291.2285842308866</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>200.7772229955152</v>
+        <v>175.8261050920825</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>33.29597338953057</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>83.20311793491715</v>
+        <v>60.90468232835936</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.17187226816797</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.30999559483051</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.987458264023044</v>
+        <v>1.931097734253476</v>
       </c>
       <c r="C2" t="n">
-        <v>7.142214548395546</v>
+        <v>8.53825978383451</v>
       </c>
       <c r="D2" t="n">
-        <v>12.33467815615692</v>
+        <v>18.5756483120539</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.544731107136738</v>
+        <v>8.290859362364314</v>
       </c>
       <c r="C3" t="n">
-        <v>21.61808444751476</v>
+        <v>26.82134728002286</v>
       </c>
       <c r="D3" t="n">
-        <v>45.60708960078558</v>
+        <v>74.17103905584652</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.31298189567226</v>
+        <v>25.46162670964103</v>
       </c>
       <c r="C4" t="n">
-        <v>70.30982533504381</v>
+        <v>94.98016339506192</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4838253295363</v>
+        <v>172.6413155395059</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.4612101034803</v>
+        <v>47.90928796724435</v>
       </c>
       <c r="C5" t="n">
-        <v>157.8895745354933</v>
+        <v>241.166323548229</v>
       </c>
       <c r="D5" t="n">
-        <v>142.991553123548</v>
+        <v>173.0821202587127</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.09193409796327</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="C6" t="n">
-        <v>284.9414719328901</v>
+        <v>386.8586646061599</v>
       </c>
       <c r="D6" t="n">
-        <v>97.04674231250146</v>
+        <v>101.7561860497734</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>25.27214940272139</v>
       </c>
       <c r="C7" t="n">
-        <v>343.6892545550191</v>
+        <v>374.8302917337279</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35896947351839</v>
+        <v>52.81998998388688</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>277.9671362419206</v>
+        <v>251.8477385704343</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>145.1062376784955</v>
+        <v>111.6031155233689</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>56.22959976073607</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.288273972150068</v>
+        <v>4.215624642035804</v>
       </c>
       <c r="C2" t="n">
-        <v>8.810203897910876</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5895316486336</v>
+        <v>15.20629019107884</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.135301256736813</v>
+        <v>1.426479414270615</v>
       </c>
       <c r="C2" t="n">
-        <v>4.05658151394782</v>
+        <v>5.123741268464104</v>
       </c>
       <c r="D2" t="n">
-        <v>9.078221021170256</v>
+        <v>13.96830633602362</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.68632376072653</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C3" t="n">
-        <v>26.75262494072558</v>
+        <v>33.18307240354219</v>
       </c>
       <c r="D3" t="n">
-        <v>50.89380098815465</v>
+        <v>80.75856615134262</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.701836102012</v>
+        <v>35.81219275551515</v>
       </c>
       <c r="C4" t="n">
-        <v>98.64306407960677</v>
+        <v>137.3779197506647</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4785567381166</v>
+        <v>174.9386051674434</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.19503330244241</v>
+        <v>28.12707172667112</v>
       </c>
       <c r="C5" t="n">
-        <v>237.5829444277282</v>
+        <v>340.0283173658828</v>
       </c>
       <c r="D5" t="n">
-        <v>133.3213382367169</v>
+        <v>153.9625837185061</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15349679922777</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>285.0219752446383</v>
+        <v>311.3465581863123</v>
       </c>
       <c r="D6" t="n">
-        <v>78.12846405166543</v>
+        <v>79.45676869551137</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>195.4698949063569</v>
+        <v>177.0847056489269</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>106.8975987769139</v>
+        <v>82.19682653806419</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
         <v>19.07535789351553</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.63727743324319</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.735370088209866</v>
+        <v>6.680793127399544</v>
       </c>
       <c r="C2" t="n">
-        <v>5.552765015219959</v>
+        <v>8.31638480267473</v>
       </c>
       <c r="D2" t="n">
-        <v>13.72974164389164</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.115527433931634</v>
+        <v>8.963356539773379</v>
       </c>
       <c r="C3" t="n">
-        <v>22.19731559302038</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="D3" t="n">
-        <v>12.87071240267569</v>
+        <v>15.90922154731956</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39776373172912</v>
+        <v>13.39778646974187</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14123365434654</v>
+        <v>70.14135269453097</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576207497850484</v>
+        <v>1.576210172910808</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.754203221039802</v>
+        <v>5.000041057729005</v>
       </c>
       <c r="C2" t="n">
-        <v>4.592615760466579</v>
+        <v>8.773879232853744</v>
       </c>
       <c r="D2" t="n">
-        <v>14.9579080219044</v>
+        <v>27.57042077836317</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50179625005713</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C3" t="n">
-        <v>21.85861263505523</v>
+        <v>25.13274122871834</v>
       </c>
       <c r="D3" t="n">
-        <v>21.29410770511332</v>
+        <v>27.11096285277567</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.73344765053038</v>
+        <v>10.55476956835746</v>
       </c>
       <c r="C4" t="n">
-        <v>34.37000537797658</v>
+        <v>20.27996232662636</v>
       </c>
       <c r="D4" t="n">
-        <v>21.81148874525138</v>
+        <v>23.40682876465245</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44080662144571</v>
+        <v>15.44054342764113</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14344746701292</v>
+        <v>86.14197912262949</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250696130830676</v>
+        <v>3.25064072160866</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.427101309076368</v>
+        <v>4.494440990041897</v>
       </c>
       <c r="C2" t="n">
-        <v>5.711808143307943</v>
+        <v>5.355433726666351</v>
       </c>
       <c r="D2" t="n">
-        <v>18.52852442225005</v>
+        <v>25.22208026980481</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.09298829446296</v>
+        <v>17.3425731955199</v>
       </c>
       <c r="C3" t="n">
-        <v>19.43860454408685</v>
+        <v>30.59616720285184</v>
       </c>
       <c r="D3" t="n">
-        <v>28.31851252899925</v>
+        <v>42.87292224445821</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.56899706230242</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="C4" t="n">
-        <v>46.36696232387261</v>
+        <v>45.37147015176634</v>
       </c>
       <c r="D4" t="n">
-        <v>27.58023825540564</v>
+        <v>31.72812230584842</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.964739198105127</v>
+        <v>9.645671194224914</v>
       </c>
       <c r="C5" t="n">
-        <v>38.50905369908114</v>
+        <v>23.66011967234813</v>
       </c>
       <c r="D5" t="n">
-        <v>30.26237298340794</v>
+        <v>31.07231483941155</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73556329958457</v>
+        <v>16.73210437850671</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0869361274659</v>
+        <v>102.0658367088909</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020668989875372</v>
+        <v>4.183026094626677</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.574944301790136</v>
+        <v>4.858669388317464</v>
       </c>
       <c r="C2" t="n">
-        <v>8.35663645854885</v>
+        <v>5.347579745032376</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89181213055037</v>
+        <v>21.75847436922206</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56208377064369</v>
+        <v>16.42463909204914</v>
       </c>
       <c r="C3" t="n">
-        <v>21.00449213236051</v>
+        <v>24.91675673378405</v>
       </c>
       <c r="D3" t="n">
-        <v>36.09886308515522</v>
+        <v>52.50386722311941</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.77243982125977</v>
+        <v>28.72888306937441</v>
       </c>
       <c r="C4" t="n">
-        <v>47.19653913396116</v>
+        <v>62.79258316362599</v>
       </c>
       <c r="D4" t="n">
-        <v>35.1357685872891</v>
+        <v>45.30765655099029</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.05848825609409</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="C5" t="n">
-        <v>64.45173678380311</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="D5" t="n">
-        <v>32.98672286269284</v>
+        <v>34.9993056563988</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781152377410974</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>37.91705983342032</v>
+        <v>25.23778823307276</v>
       </c>
       <c r="D6" t="n">
         <v>38.52083467153211</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06352037220301</v>
+        <v>18.05516225274351</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8429662377053</v>
+        <v>117.7884394583743</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881341094172574</v>
+        <v>6.01838741758117</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.818417732443345</v>
+        <v>4.98924183298229</v>
       </c>
       <c r="C2" t="n">
-        <v>8.929977117828987</v>
+        <v>8.404742096056944</v>
       </c>
       <c r="D2" t="n">
-        <v>23.27429282457913</v>
+        <v>20.9288975591335</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28933783531232</v>
+        <v>14.72621556370216</v>
       </c>
       <c r="C3" t="n">
-        <v>25.90341317655209</v>
+        <v>21.17138924208247</v>
       </c>
       <c r="D3" t="n">
-        <v>43.48651455961247</v>
+        <v>53.97158004096841</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.87981017392116</v>
+        <v>22.01569226773472</v>
       </c>
       <c r="C4" t="n">
-        <v>41.64475586644545</v>
+        <v>52.32715263635499</v>
       </c>
       <c r="D4" t="n">
-        <v>38.76038111136832</v>
+        <v>52.83766144256334</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.89235190989812</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="C5" t="n">
-        <v>57.18680377237672</v>
+        <v>65.16350386938205</v>
       </c>
       <c r="D5" t="n">
-        <v>31.04777114680538</v>
+        <v>34.50843180427539</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58618549489336</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>48.5434969841878</v>
+        <v>39.64788103600744</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060864968469993</v>
+        <v>7.055771217384907</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19560907940618</v>
+        <v>66.14785516298349</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295648726352495</v>
+        <v>4.409857010865566</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.226423866782518</v>
+        <v>5.454590244795278</v>
       </c>
       <c r="C2" t="n">
-        <v>6.052474596681586</v>
+        <v>9.453248644192538</v>
       </c>
       <c r="D2" t="n">
-        <v>24.75967710110456</v>
+        <v>23.83094377288708</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.93376523992573</v>
+        <v>16.47372647726148</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80862561759665</v>
+        <v>28.69648539513427</v>
       </c>
       <c r="D3" t="n">
-        <v>53.04382846045517</v>
+        <v>58.5121631731099</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.30847406777853</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C4" t="n">
-        <v>56.56437572788423</v>
+        <v>52.87594960302896</v>
       </c>
       <c r="D4" t="n">
-        <v>53.27159392784043</v>
+        <v>68.35712915129692</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.04085785514665</v>
+        <v>27.90617849321559</v>
       </c>
       <c r="C5" t="n">
-        <v>69.60591223109887</v>
+        <v>84.55302102825655</v>
       </c>
       <c r="D5" t="n">
-        <v>38.85266539556753</v>
+        <v>46.97662764820988</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.6365166697172</v>
+        <v>20.20633124880786</v>
       </c>
       <c r="C6" t="n">
-        <v>73.98254349663115</v>
+        <v>76.84041106369361</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>51.50248456478767</v>
+        <v>41.56130731158447</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>22.61455836732527</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
         <v>31.06249736236907</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285198331677115</v>
+        <v>7.277606030599955</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58393269115008</v>
+        <v>75.50516256747454</v>
       </c>
       <c r="D21" t="n">
-        <v>6.374548540217476</v>
+        <v>5.458204522949966</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.080724295926491</v>
+        <v>4.191080949429634</v>
       </c>
       <c r="C2" t="n">
-        <v>4.69079053089126</v>
+        <v>13.44601655736431</v>
       </c>
       <c r="D2" t="n">
-        <v>19.8509385798705</v>
+        <v>30.52842661125882</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37416904850505</v>
+        <v>17.84817326320701</v>
       </c>
       <c r="C3" t="n">
-        <v>26.80171232593792</v>
+        <v>33.60031517784709</v>
       </c>
       <c r="D3" t="n">
-        <v>60.54438092090079</v>
+        <v>64.00013283984957</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.49915410658066</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>69.64616388697297</v>
+        <v>64.08161789930206</v>
       </c>
       <c r="D4" t="n">
-        <v>67.38716241950105</v>
+        <v>82.35783316156066</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.88854809226815</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>89.95263340161401</v>
+        <v>92.16156573616934</v>
       </c>
       <c r="D5" t="n">
-        <v>49.87278337573798</v>
+        <v>60.50020227420971</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.6126359296458</v>
+        <v>29.90698031447059</v>
       </c>
       <c r="C6" t="n">
-        <v>94.71214627180255</v>
+        <v>108.5989675483737</v>
       </c>
       <c r="D6" t="n">
-        <v>39.16486116551801</v>
+        <v>43.02902012943346</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>82.46386191361933</v>
+        <v>78.87066531607601</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
         <v>32.61562223048752</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.497122388386022</v>
+        <v>7.486584812793321</v>
       </c>
       <c r="C21" t="n">
-        <v>85.27976716789101</v>
+        <v>84.22407914392487</v>
       </c>
       <c r="D21" t="n">
-        <v>7.497122388386022</v>
+        <v>6.550761711194157</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_62_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497642595035</v>
+        <v>10.84497652494834</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907226852798</v>
+        <v>37.7890726134842</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.644067551714913</v>
+        <v>1.107411410390402</v>
       </c>
       <c r="C2" t="n">
-        <v>13.20352487441535</v>
+        <v>2.555489274154447</v>
       </c>
       <c r="D2" t="n">
-        <v>34.38571334124453</v>
+        <v>10.59207598111884</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.90431280879833</v>
+        <v>9.699667317958486</v>
       </c>
       <c r="C3" t="n">
-        <v>43.8792136413112</v>
+        <v>40.08475876439726</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35971454151115</v>
+        <v>47.96819282949916</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.02166486941822</v>
+        <v>17.75294373589507</v>
       </c>
       <c r="C4" t="n">
-        <v>74.81506554983244</v>
+        <v>121.6159603589821</v>
       </c>
       <c r="D4" t="n">
-        <v>93.57626417798897</v>
+        <v>54.96903570848316</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.85895679242051</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="C5" t="n">
-        <v>104.8506548135594</v>
+        <v>112.6555490623215</v>
       </c>
       <c r="D5" t="n">
-        <v>75.57002953439824</v>
+        <v>39.61351986635881</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>128.2417756149439</v>
+        <v>65.00642423670256</v>
       </c>
       <c r="D6" t="n">
-        <v>51.15985461600555</v>
+        <v>29.7057220351</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>117.737075179503</v>
+        <v>35.39298648580176</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>73.1009340582175</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>38.82812170296133</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.15071578703105</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.680234074466925</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.12283815291146</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.680234074466925</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.915029918087032</v>
+        <v>1.02788984634641</v>
       </c>
       <c r="C2" t="n">
-        <v>12.43677991739859</v>
+        <v>6.71908128786517</v>
       </c>
       <c r="D2" t="n">
-        <v>36.89015173477815</v>
+        <v>16.63669659616645</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.24930716361646</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="C3" t="n">
-        <v>47.35950925286613</v>
+        <v>22.19240685449915</v>
       </c>
       <c r="D3" t="n">
-        <v>81.03836424705297</v>
+        <v>45.7690779719863</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.8092064546734</v>
+        <v>18.55699510567321</v>
       </c>
       <c r="C4" t="n">
-        <v>91.01095742679206</v>
+        <v>110.5634447045715</v>
       </c>
       <c r="D4" t="n">
-        <v>106.1603062510246</v>
+        <v>65.48551711637499</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.81049130201392</v>
+        <v>22.99743997198154</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6322491593268</v>
+        <v>174.3093048890212</v>
       </c>
       <c r="D5" t="n">
-        <v>88.57818661566847</v>
+        <v>50.82998738737862</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.12210623488766</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>145.0267161144516</v>
+        <v>125.8266762624967</v>
       </c>
       <c r="D6" t="n">
-        <v>61.62528514327655</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.03366682604743</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>149.8961847275158</v>
+        <v>65.75549773504287</v>
       </c>
       <c r="D7" t="n">
-        <v>44.97484407925062</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.36144738607885</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>110.652783745658</v>
+        <v>38.21943812632832</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>62.79061966821748</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.857108752642118</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1602751902673</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.839247346722383</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.942518853805943</v>
+        <v>0.5448699758569798</v>
       </c>
       <c r="C2" t="n">
-        <v>19.20102159965912</v>
+        <v>2.778346003018473</v>
       </c>
       <c r="D2" t="n">
-        <v>41.71151471033424</v>
+        <v>11.21548577331556</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>5.870851271395926</v>
       </c>
       <c r="C3" t="n">
-        <v>47.34478303730243</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="D3" t="n">
-        <v>88.25911861178827</v>
+        <v>49.31318718431729</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.93683365622549</v>
+        <v>20.3437759274024</v>
       </c>
       <c r="C4" t="n">
-        <v>101.8082186780985</v>
+        <v>98.61753863929636</v>
       </c>
       <c r="D4" t="n">
-        <v>116.957567502331</v>
+        <v>72.79855576530949</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.47317100238052</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="C5" t="n">
-        <v>139.4081740030471</v>
+        <v>206.4369985104981</v>
       </c>
       <c r="D5" t="n">
-        <v>102.5190040159732</v>
+        <v>57.92311455056183</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.15985461600555</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="C6" t="n">
-        <v>165.0317890838888</v>
+        <v>167.4871400922101</v>
       </c>
       <c r="D6" t="n">
-        <v>71.44668917656163</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.4596064609703</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>174.1502617609332</v>
+        <v>64.61765214582081</v>
       </c>
       <c r="D7" t="n">
-        <v>50.90361846519711</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.37112599440107</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>147.0363536650448</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>94.07499201174633</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.016516919436517</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2250430273226</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02064614929565</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.589089680277091</v>
+        <v>1.063232763699296</v>
       </c>
       <c r="C2" t="n">
-        <v>13.36354975020758</v>
+        <v>4.378594760940774</v>
       </c>
       <c r="D2" t="n">
-        <v>34.21587098840983</v>
+        <v>8.888743714250621</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.33828635180442</v>
+        <v>3.750276230222816</v>
       </c>
       <c r="C3" t="n">
-        <v>71.97192419833367</v>
+        <v>17.11186248502191</v>
       </c>
       <c r="D3" t="n">
-        <v>94.30668446994861</v>
+        <v>46.86863540074273</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.36479353981909</v>
+        <v>16.06826467540754</v>
       </c>
       <c r="C4" t="n">
-        <v>124.3216570318863</v>
+        <v>80.1626452948648</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1925650565445</v>
+        <v>81.38786642976483</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.81429511964389</v>
+        <v>27.61165418194155</v>
       </c>
       <c r="C5" t="n">
-        <v>98.61655689159213</v>
+        <v>197.5521817870645</v>
       </c>
       <c r="D5" t="n">
-        <v>70.24404823885929</v>
+        <v>69.53228115328035</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.3648345975481</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="C6" t="n">
-        <v>114.6769675853657</v>
+        <v>247.8696968728262</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>103.3642887893297</v>
+        <v>149.057772188089</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>69.34574908947344</v>
+        <v>61.2512392679585</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.446916189610551</v>
+        <v>0.6852598975642736</v>
       </c>
       <c r="C2" t="n">
-        <v>6.304783756673016</v>
+        <v>2.471058971589222</v>
       </c>
       <c r="D2" t="n">
-        <v>24.24229606096649</v>
+        <v>6.872233929727672</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.89649988489336</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="C3" t="n">
-        <v>63.3423618780042</v>
+        <v>17.30821202587127</v>
       </c>
       <c r="D3" t="n">
-        <v>100.2168056495144</v>
+        <v>43.83503499462009</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.43083267791088</v>
+        <v>12.83929647613979</v>
       </c>
       <c r="C4" t="n">
-        <v>154.8373209229899</v>
+        <v>64.01780429852602</v>
       </c>
       <c r="D4" t="n">
-        <v>129.8351521389364</v>
+        <v>85.90586936470865</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.80862561759666</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="C5" t="n">
-        <v>155.6315548157257</v>
+        <v>182.6787040677253</v>
       </c>
       <c r="D5" t="n">
-        <v>88.52909923045614</v>
+        <v>80.42968067041996</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.91327171132357</v>
+        <v>27.57238427377167</v>
       </c>
       <c r="C6" t="n">
-        <v>137.4996564659913</v>
+        <v>288.2018560586937</v>
       </c>
       <c r="D6" t="n">
-        <v>41.13719230334986</v>
+        <v>52.64916588334796</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>128.516664972133</v>
+        <v>223.7962614169901</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>91.79341034707677</v>
+        <v>96.71687508387453</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4874963073167</v>
+        <v>48.03593342109217</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.295727043156542</v>
+        <v>0.7461282552275759</v>
       </c>
       <c r="C2" t="n">
-        <v>6.843763246304515</v>
+        <v>6.102543729598173</v>
       </c>
       <c r="D2" t="n">
-        <v>19.86664654313845</v>
+        <v>9.02422489743668</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.33137306014569</v>
+        <v>3.05323536020758</v>
       </c>
       <c r="C3" t="n">
-        <v>43.61905049968578</v>
+        <v>13.17996292951343</v>
       </c>
       <c r="D3" t="n">
-        <v>96.33399347921828</v>
+        <v>39.5987936507951</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>10.10807436292516</v>
       </c>
       <c r="C4" t="n">
-        <v>156.2412201400629</v>
+        <v>53.9863062565321</v>
       </c>
       <c r="D4" t="n">
-        <v>147.2179769903304</v>
+        <v>87.87132826861075</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.23278168356029</v>
+        <v>24.91184799526282</v>
       </c>
       <c r="C5" t="n">
-        <v>216.5244561716341</v>
+        <v>151.4100396874643</v>
       </c>
       <c r="D5" t="n">
-        <v>110.569335190797</v>
+        <v>90.98346849107317</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>32.48308629041422</v>
       </c>
       <c r="C6" t="n">
-        <v>188.377749490878</v>
+        <v>290.4559487876444</v>
       </c>
       <c r="D6" t="n">
-        <v>55.54728510628455</v>
+        <v>63.35610634586367</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.61339669317178</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>159.7175887608009</v>
+        <v>314.2849290651229</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>126.8418033886879</v>
+        <v>184.0040634684584</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>78.4328058399819</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.998838325846506</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.344814428368883</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="D2" t="n">
-        <v>13.85933234085222</v>
+        <v>6.497206306705391</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80122929985241</v>
+        <v>4.138066573400306</v>
       </c>
       <c r="C3" t="n">
-        <v>39.42207906403067</v>
+        <v>19.04099672386689</v>
       </c>
       <c r="D3" t="n">
-        <v>94.48339905671304</v>
+        <v>43.245986372072</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.49687181600267</v>
+        <v>16.85955332503048</v>
       </c>
       <c r="C4" t="n">
-        <v>154.8245582028347</v>
+        <v>77.81430478630644</v>
       </c>
       <c r="D4" t="n">
-        <v>159.8275445036765</v>
+        <v>90.57702494151498</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.60722846950583</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="C5" t="n">
-        <v>268.3116475706533</v>
+        <v>236.257585026995</v>
       </c>
       <c r="D5" t="n">
-        <v>116.1407534123977</v>
+        <v>85.41205026947252</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>216.8759218497544</v>
+        <v>278.1389420901639</v>
       </c>
       <c r="D6" t="n">
-        <v>53.65545728020094</v>
+        <v>56.99634471775284</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="C7" t="n">
-        <v>165.0474970471568</v>
+        <v>129.3550775115597</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>89.62374792069132</v>
+        <v>57.74639996379738</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.525055095322796</v>
+        <v>0.2719441140763665</v>
       </c>
       <c r="C2" t="n">
-        <v>9.393362034233482</v>
+        <v>3.092505268377453</v>
       </c>
       <c r="D2" t="n">
-        <v>17.621389543526</v>
+        <v>4.914629007459533</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.59934912567607</v>
+        <v>2.896155727528091</v>
       </c>
       <c r="C3" t="n">
-        <v>26.34519964346316</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="D3" t="n">
-        <v>85.05862109594365</v>
+        <v>38.59250225394211</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.34447993766616</v>
+        <v>11.74170254279185</v>
       </c>
       <c r="C4" t="n">
-        <v>129.4777959745906</v>
+        <v>59.86992024808324</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1488380448725</v>
+        <v>87.80751466783472</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.23402547317179</v>
+        <v>18.28505099159685</v>
       </c>
       <c r="C5" t="n">
-        <v>277.7364255314227</v>
+        <v>173.1066639513189</v>
       </c>
       <c r="D5" t="n">
-        <v>141.2489509485099</v>
+        <v>87.67006998924018</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.79630486579796</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="C6" t="n">
-        <v>304.9465449023273</v>
+        <v>267.7942665305152</v>
       </c>
       <c r="D6" t="n">
-        <v>70.03788122096746</v>
+        <v>58.80766923208819</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>226.910365134861</v>
+        <v>182.4745005452419</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>138.1073582949201</v>
+        <v>67.92712365683681</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.715113239319178</v>
+        <v>0.4535674393620264</v>
       </c>
       <c r="C2" t="n">
-        <v>5.579272203234622</v>
+        <v>3.4626241528785</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17407244328795</v>
+        <v>10.82671368243382</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.44579557318606</v>
+        <v>1.786780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>31.20485077948487</v>
+        <v>13.45976102522377</v>
       </c>
       <c r="D3" t="n">
-        <v>80.90582830697964</v>
+        <v>33.56595400819845</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.33698580893068</v>
+        <v>8.53825978383451</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6790699494944</v>
+        <v>47.31140361535804</v>
       </c>
       <c r="D4" t="n">
-        <v>172.8710445022996</v>
+        <v>87.53949754457535</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.866491978885</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="C5" t="n">
-        <v>270.569667290421</v>
+        <v>139.4327176956533</v>
       </c>
       <c r="D5" t="n">
-        <v>155.7788169713627</v>
+        <v>99.79465413668829</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>359.8900551705</v>
+        <v>273.107485105899</v>
       </c>
       <c r="D6" t="n">
-        <v>82.95866275655973</v>
+        <v>72.65423885278521</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>291.2285842308866</v>
+        <v>294.2229147288393</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>42.75903951076558</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>175.8261050920825</v>
+        <v>157.968114351833</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.30999559483051</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.931097734253476</v>
+        <v>0.5811946409141118</v>
       </c>
       <c r="C2" t="n">
-        <v>8.53825978383451</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D2" t="n">
-        <v>18.5756483120539</v>
+        <v>10.39474469256523</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.290859362364314</v>
+        <v>1.649336143134642</v>
       </c>
       <c r="C3" t="n">
-        <v>26.82134728002286</v>
+        <v>13.4204911170539</v>
       </c>
       <c r="D3" t="n">
-        <v>74.17103905584652</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.46162670964103</v>
+        <v>5.92190215201676</v>
       </c>
       <c r="C4" t="n">
-        <v>94.98016339506192</v>
+        <v>39.93455136564751</v>
       </c>
       <c r="D4" t="n">
-        <v>172.6413155395059</v>
+        <v>83.99146134142737</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.90928796724435</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C5" t="n">
-        <v>241.166323548229</v>
+        <v>110.9865779651019</v>
       </c>
       <c r="D5" t="n">
-        <v>173.0821202587127</v>
+        <v>108.6058397823034</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.95230493978197</v>
+        <v>21.9774041072691</v>
       </c>
       <c r="C6" t="n">
-        <v>386.8586646061599</v>
+        <v>248.4332200550639</v>
       </c>
       <c r="D6" t="n">
-        <v>101.7561860497734</v>
+        <v>86.50080847348222</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.27214940272139</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>374.8302917337279</v>
+        <v>347.881317252153</v>
       </c>
       <c r="D7" t="n">
-        <v>52.81998998388688</v>
+        <v>52.10135066437822</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>251.8477385704343</v>
+        <v>273.9616056085937</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>111.6031155233689</v>
+        <v>124.8046769023757</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.215624642035804</v>
+        <v>4.978442608235575</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>5.360342465187585</v>
       </c>
       <c r="D2" t="n">
-        <v>15.20629019107884</v>
+        <v>7.341509332357648</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.426479414270615</v>
+        <v>0.9876381904722912</v>
       </c>
       <c r="C2" t="n">
-        <v>5.123741268464104</v>
+        <v>8.099418560036186</v>
       </c>
       <c r="D2" t="n">
-        <v>13.96830633602362</v>
+        <v>10.97692108118359</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.09865779651019</v>
+        <v>1.781872083207961</v>
       </c>
       <c r="C3" t="n">
-        <v>33.18307240354219</v>
+        <v>27.23859005432776</v>
       </c>
       <c r="D3" t="n">
-        <v>80.75856615134262</v>
+        <v>34.32680847898973</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.81219275551515</v>
+        <v>4.518002934943822</v>
       </c>
       <c r="C4" t="n">
-        <v>137.3779197506647</v>
+        <v>36.34822700203391</v>
       </c>
       <c r="D4" t="n">
-        <v>174.9386051674434</v>
+        <v>82.2429686801638</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.12707172667112</v>
+        <v>12.98361338866407</v>
       </c>
       <c r="C5" t="n">
-        <v>340.0283173658828</v>
+        <v>92.92242020696061</v>
       </c>
       <c r="D5" t="n">
-        <v>153.9625837185061</v>
+        <v>112.3855684436536</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.65789413503238</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>311.3465581863123</v>
+        <v>216.7149152262579</v>
       </c>
       <c r="D6" t="n">
-        <v>79.45676869551137</v>
+        <v>99.38133835320039</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>177.0847056489269</v>
+        <v>353.6903184181814</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>62.82105384704915</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>82.19682653806419</v>
+        <v>362.6674194258142</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>220.8765437445601</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>89.82500620006192</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>15.63727743324319</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.680793127399544</v>
+        <v>5.137485736323558</v>
       </c>
       <c r="C2" t="n">
-        <v>8.31638480267473</v>
+        <v>9.251990364821941</v>
       </c>
       <c r="D2" t="n">
-        <v>17.91689560250429</v>
+        <v>9.554368657729958</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.963356539773379</v>
+        <v>8.222137023067038</v>
       </c>
       <c r="C3" t="n">
-        <v>12.93452600345173</v>
+        <v>10.58324025178062</v>
       </c>
       <c r="D3" t="n">
-        <v>15.90922154731956</v>
+        <v>8.060148651866312</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39778646974187</v>
+        <v>11.67866599062078</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14135269453097</v>
+        <v>59.95048541852004</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576210172910808</v>
+        <v>0.7785777327080524</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.000041057729005</v>
+        <v>2.707660168312703</v>
       </c>
       <c r="C2" t="n">
-        <v>8.773879232853744</v>
+        <v>5.649958037940394</v>
       </c>
       <c r="D2" t="n">
-        <v>27.57042077836317</v>
+        <v>10.63036414158446</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36711688812607</v>
+        <v>14.31879026643973</v>
       </c>
       <c r="C3" t="n">
-        <v>25.13274122871834</v>
+        <v>27.60674544342031</v>
       </c>
       <c r="D3" t="n">
-        <v>27.11096285277567</v>
+        <v>14.44150872947058</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.55476956835746</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C4" t="n">
-        <v>20.27996232662636</v>
+        <v>17.76570645605028</v>
       </c>
       <c r="D4" t="n">
-        <v>23.40682876465245</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44054342764113</v>
+        <v>13.63217238916735</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14197912262949</v>
+        <v>73.77410940019978</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25064072160866</v>
+        <v>1.603784986960865</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.494440990041897</v>
+        <v>1.9546596791554</v>
       </c>
       <c r="C2" t="n">
-        <v>5.355433726666351</v>
+        <v>4.939172700065703</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22208026980481</v>
+        <v>16.58073697702438</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3425731955199</v>
+        <v>11.59444038715483</v>
       </c>
       <c r="C3" t="n">
-        <v>30.59616720285184</v>
+        <v>24.04300127700439</v>
       </c>
       <c r="D3" t="n">
-        <v>42.87292224445821</v>
+        <v>19.88039101099791</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.61103228713579</v>
+        <v>20.75218297236908</v>
       </c>
       <c r="C4" t="n">
-        <v>45.37147015176634</v>
+        <v>50.05538844872788</v>
       </c>
       <c r="D4" t="n">
-        <v>31.72812230584842</v>
+        <v>21.5307089018368</v>
       </c>
     </row>
     <row r="5">
@@ -5179,10 +5179,10 @@
         <v>9.645671194224914</v>
       </c>
       <c r="C5" t="n">
-        <v>23.66011967234813</v>
+        <v>21.99114857512856</v>
       </c>
       <c r="D5" t="n">
-        <v>31.07231483941155</v>
+        <v>26.70353755551325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73210437850671</v>
+        <v>14.84765179207302</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0658367088909</v>
+        <v>87.43617166443002</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183026094626677</v>
+        <v>2.47460863201217</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.858669388317464</v>
+        <v>1.213440162449058</v>
       </c>
       <c r="C2" t="n">
-        <v>5.347579745032376</v>
+        <v>9.074294030353268</v>
       </c>
       <c r="D2" t="n">
-        <v>21.75847436922206</v>
+        <v>18.04844979487336</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42463909204914</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C3" t="n">
-        <v>24.91675673378405</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="D3" t="n">
-        <v>52.50386722311941</v>
+        <v>28.52958828541231</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.72888306937441</v>
+        <v>21.84977690571701</v>
       </c>
       <c r="C4" t="n">
-        <v>62.79258316362599</v>
+        <v>56.18149412322797</v>
       </c>
       <c r="D4" t="n">
-        <v>45.30765655099029</v>
+        <v>26.45711888174729</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.38384765682728</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>56.13142499031139</v>
+        <v>62.88094045700822</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9993056563988</v>
+        <v>28.69157665661304</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.620145753914496</v>
+        <v>9.137125883425066</v>
       </c>
       <c r="C6" t="n">
-        <v>25.23778823307276</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="D6" t="n">
-        <v>38.52083467153211</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05516225274351</v>
+        <v>16.09787056805405</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7884394583743</v>
+        <v>101.6707614824467</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01838741758117</v>
+        <v>3.389025382748222</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98924183298229</v>
+        <v>3.128829933434584</v>
       </c>
       <c r="C2" t="n">
-        <v>8.404742096056944</v>
+        <v>13.70519795128547</v>
       </c>
       <c r="D2" t="n">
-        <v>20.9288975591335</v>
+        <v>18.12404436810036</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.72621556370216</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C3" t="n">
-        <v>21.17138924208247</v>
+        <v>29.38861752662827</v>
       </c>
       <c r="D3" t="n">
-        <v>53.97158004096841</v>
+        <v>35.89760480578462</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.01569226773472</v>
+        <v>19.45038551653781</v>
       </c>
       <c r="C4" t="n">
-        <v>52.32715263635499</v>
+        <v>53.71828913327272</v>
       </c>
       <c r="D4" t="n">
-        <v>52.83766144256334</v>
+        <v>34.10198825471721</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.2240027074843</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="C5" t="n">
-        <v>65.16350386938205</v>
+        <v>85.82929304377741</v>
       </c>
       <c r="D5" t="n">
-        <v>34.50843180427539</v>
+        <v>31.857713002809</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.82769543013807</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C6" t="n">
-        <v>39.64788103600744</v>
+        <v>64.76491430145784</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>35.30070220160257</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>18.68462230722529</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055771217384907</v>
+        <v>17.37704841444341</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14785516298349</v>
+        <v>115.5573719560487</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409857010865566</v>
+        <v>4.344262103610853</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.454590244795278</v>
+        <v>2.421971586376881</v>
       </c>
       <c r="C2" t="n">
-        <v>9.453248644192538</v>
+        <v>10.2033038902371</v>
       </c>
       <c r="D2" t="n">
-        <v>23.83094377288708</v>
+        <v>19.56230475482194</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47372647726148</v>
+        <v>8.555931242510953</v>
       </c>
       <c r="C3" t="n">
-        <v>28.69648539513427</v>
+        <v>42.57839793318416</v>
       </c>
       <c r="D3" t="n">
-        <v>58.5121631731099</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.4698816019025</v>
+        <v>15.49394226842316</v>
       </c>
       <c r="C4" t="n">
-        <v>52.87594960302896</v>
+        <v>64.36239774271664</v>
       </c>
       <c r="D4" t="n">
-        <v>68.35712915129692</v>
+        <v>42.97207876258713</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.90617849321559</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="C5" t="n">
-        <v>84.55302102825655</v>
+        <v>91.94067250271381</v>
       </c>
       <c r="D5" t="n">
-        <v>46.97662764820988</v>
+        <v>36.69282044622454</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.20633124880786</v>
+        <v>28.09565580013523</v>
       </c>
       <c r="C6" t="n">
-        <v>76.84041106369361</v>
+        <v>101.273166179284</v>
       </c>
       <c r="D6" t="n">
-        <v>36.06548366321083</v>
+        <v>37.23278168356029</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="C7" t="n">
-        <v>41.56130731158447</v>
+        <v>60.12615639889166</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>22.61455836732527</v>
+        <v>30.54217107911827</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>46.7341359652609</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277606030599955</v>
+        <v>18.67780952031607</v>
       </c>
       <c r="C21" t="n">
-        <v>75.50516256747454</v>
+        <v>128.9658276402776</v>
       </c>
       <c r="D21" t="n">
-        <v>5.458204522949966</v>
+        <v>5.336517005804592</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.191080949429634</v>
+        <v>2.199114857512855</v>
       </c>
       <c r="C2" t="n">
-        <v>13.44601655736431</v>
+        <v>6.202681995431348</v>
       </c>
       <c r="D2" t="n">
-        <v>30.52842661125882</v>
+        <v>15.25930456710817</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84817326320701</v>
+        <v>11.05447914981909</v>
       </c>
       <c r="C3" t="n">
-        <v>33.60031517784709</v>
+        <v>58.74778262212914</v>
       </c>
       <c r="D3" t="n">
-        <v>64.00013283984957</v>
+        <v>46.20595570037614</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>13.7582123273148</v>
       </c>
       <c r="C4" t="n">
-        <v>64.08161789930206</v>
+        <v>86.67163257402116</v>
       </c>
       <c r="D4" t="n">
-        <v>82.35783316156066</v>
+        <v>41.92553570986004</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C5" t="n">
-        <v>92.16156573616934</v>
+        <v>60.50020227420971</v>
       </c>
       <c r="D5" t="n">
-        <v>60.50020227420971</v>
+        <v>33.15852871093603</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.90698031447059</v>
+        <v>9.660397409788615</v>
       </c>
       <c r="C6" t="n">
-        <v>108.5989675483737</v>
+        <v>39.56737772425921</v>
       </c>
       <c r="D6" t="n">
-        <v>43.02902012943346</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>78.87066531607601</v>
+        <v>21.43940636534185</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>40.55599766243574</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.62499773917349</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486584812793321</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22407914392487</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.550761711194157</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
